--- a/out/test_video/costco_price_cards_test_final.xlsx
+++ b/out/test_video/costco_price_cards_test_final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,11 +459,11 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16599</t>
+          <t>16595</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1698</v>
+        <v>11335</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -472,11 +472,11 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20977</t>
+          <t>16600</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1799</v>
+        <v>1508</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2380</v>
+        <v>2330</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -511,11 +511,11 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>32999</t>
+          <t>32994</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1680</v>
+        <v>680</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -524,11 +524,11 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>38610</t>
+          <t>39222</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1398</v>
+        <v>1799</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -537,11 +537,11 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>387906</t>
+          <t>51982</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2998</v>
+        <v>1928</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -550,11 +550,11 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>51982</t>
+          <t>557900</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1928</v>
+        <v>2998</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -563,11 +563,11 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>52201</t>
+          <t>570239</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>948</v>
+        <v>1280</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -576,11 +576,11 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>55561</t>
+          <t>57357</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>848</v>
+        <v>3098</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
@@ -589,11 +589,11 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>570239</t>
+          <t>583950</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1280</v>
+        <v>1098</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
@@ -602,11 +602,11 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>57357</t>
+          <t>58610</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2398</v>
+        <v>1398</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
@@ -615,11 +615,11 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>583950</t>
+          <t>587821</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1098</v>
+        <v>548</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
@@ -628,11 +628,11 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>58610</t>
+          <t>587906</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1398</v>
+        <v>2998</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
@@ -641,11 +641,11 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>587821</t>
+          <t>70909</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>548</v>
+        <v>11235</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
@@ -654,66 +654,14 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>587900</t>
+          <t>87821</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2998</v>
+        <v>548</v>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>70909</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1298</v>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>77863</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>4389</v>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>879064</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>2995</v>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>882662</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>548</v>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
